--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.20427199436275</v>
+        <v>5.883194199083947</v>
       </c>
       <c r="D2" t="n">
-        <v>36.49397648211247</v>
+        <v>5.930271178343276</v>
       </c>
       <c r="E2" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F2" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.20651961871723</v>
+        <v>7.18355943804155</v>
       </c>
       <c r="D3" t="n">
-        <v>6.96419413859206</v>
+        <v>1.13168154752121</v>
       </c>
       <c r="E3" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F3" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.396725490830525</v>
+        <v>1.20196789225996</v>
       </c>
       <c r="D4" t="n">
-        <v>6.699027650006355</v>
+        <v>1.088591993126033</v>
       </c>
       <c r="E4" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F4" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.85041230606116</v>
+        <v>3.388191999734939</v>
       </c>
       <c r="D5" t="n">
-        <v>20.41122279542245</v>
+        <v>3.316823704256148</v>
       </c>
       <c r="E5" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F5" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.76624875461876</v>
+        <v>5.812015422625549</v>
       </c>
       <c r="D6" t="n">
-        <v>34.9271738817037</v>
+        <v>5.675665755776852</v>
       </c>
       <c r="E6" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F6" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.46972941227977</v>
+        <v>3.488831029495462</v>
       </c>
       <c r="D7" t="n">
-        <v>22.51580110048684</v>
+        <v>3.658817678829112</v>
       </c>
       <c r="E7" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F7" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.4046577543008</v>
+        <v>5.265756885073881</v>
       </c>
       <c r="D8" t="n">
-        <v>15.99071372346102</v>
+        <v>2.598490980062415</v>
       </c>
       <c r="E8" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F8" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.80892875800423</v>
+        <v>5.656450923175687</v>
       </c>
       <c r="D9" t="n">
-        <v>34.13877762804842</v>
+        <v>5.547551364557869</v>
       </c>
       <c r="E9" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F9" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>13.77012106800539</v>
+        <v>2.237644673550876</v>
       </c>
       <c r="D10" t="n">
-        <v>12.93548412804074</v>
+        <v>2.102016170806621</v>
       </c>
       <c r="E10" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F10" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.02726402077522</v>
+        <v>2.766930403375973</v>
       </c>
       <c r="D11" t="n">
-        <v>14.76751901252039</v>
+        <v>2.399721839534563</v>
       </c>
       <c r="E11" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F11" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>13.09498032142706</v>
+        <v>2.127934302231898</v>
       </c>
       <c r="D12" t="n">
-        <v>25.3009225301203</v>
+        <v>4.111399911144548</v>
       </c>
       <c r="E12" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F12" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.77053602293447</v>
+        <v>5.325212103726852</v>
       </c>
       <c r="D13" t="n">
-        <v>18.09640362645316</v>
+        <v>2.940665589298639</v>
       </c>
       <c r="E13" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F13" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.66157461948971</v>
+        <v>5.632505875667078</v>
       </c>
       <c r="D14" t="n">
-        <v>35.51878451708035</v>
+        <v>5.771802484025557</v>
       </c>
       <c r="E14" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F14" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>5.715426643828972</v>
+        <v>0.9287568296222081</v>
       </c>
       <c r="D15" t="n">
-        <v>17.50534076868419</v>
+        <v>2.844617874911181</v>
       </c>
       <c r="E15" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F15" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>24.41869970163284</v>
+        <v>3.968038701515337</v>
       </c>
       <c r="D16" t="n">
-        <v>3.03045454166684</v>
+        <v>0.4924488630208616</v>
       </c>
       <c r="E16" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F16" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>41.22545887197372</v>
+        <v>6.69913706669573</v>
       </c>
       <c r="D17" t="n">
-        <v>41.56969937704758</v>
+        <v>6.755076148770232</v>
       </c>
       <c r="E17" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F17" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>24.84705101916219</v>
+        <v>4.037645790613856</v>
       </c>
       <c r="D18" t="n">
-        <v>18.59595924878106</v>
+        <v>3.021843377926922</v>
       </c>
       <c r="E18" t="n">
-        <v>11.39454518892785</v>
+        <v>1.851613593200776</v>
       </c>
       <c r="F18" t="n">
-        <v>11.21269666067111</v>
+        <v>1.822063207359055</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
